--- a/backtest_runs/20260410_193731/by_symbol/TPLP/TPLP.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/TPLP/TPLP.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-5052.059999999998</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>111292.84</v>
@@ -679,7 +679,7 @@
         <v>-11441.42999999999</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>99851.41</v>
@@ -771,7 +771,7 @@
         <v>-3120.389999999999</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>106983.73</v>
@@ -817,7 +817,7 @@
         <v>-1485.899999999995</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>105497.83</v>
@@ -909,7 +909,7 @@
         <v>-297.1800000000069</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>105795.01</v>
@@ -955,7 +955,7 @@
         <v>-1337.309999999998</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>104457.7</v>
@@ -1001,7 +1001,7 @@
         <v>-148.5899999999968</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>104309.11</v>
@@ -1047,7 +1047,7 @@
         <v>-1485.899999999995</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>102823.21</v>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>107726.68</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>107726.68</v>
@@ -1277,7 +1277,7 @@
         <v>-5795.009999999996</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>101931.67</v>
@@ -1415,7 +1415,7 @@
         <v>-3863.339999999997</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>104160.52</v>
@@ -1461,7 +1461,7 @@
         <v>-891.5400000000074</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>103268.98</v>
@@ -1553,7 +1553,7 @@
         <v>-1040.129999999991</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>104903.47</v>
@@ -1645,7 +1645,7 @@
         <v>-4754.880000000005</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>113373.1</v>
